--- a/sheets/대금율보/검수/검정고무신.xlsx
+++ b/sheets/대금율보/검수/검정고무신.xlsx
@@ -4346,8 +4346,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌇
-‹</t>
+          <t xml:space="preserve">汰⌇</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -4426,7 +4425,7 @@
       <c r="C5" s="23"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋潕‹
+          <t xml:space="preserve">淋潕
 –潢</t>
         </is>
       </c>
@@ -4487,7 +4486,7 @@
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 㳞汰</t>
         </is>
       </c>
@@ -4519,8 +4518,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞⌇
-‹</t>
+          <t xml:space="preserve">㳞⌇</t>
         </is>
       </c>
       <c r="C7" s="22"/>
@@ -4866,8 +4864,7 @@
       <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△潢
-–無
-‹</t>
+–無</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -4926,7 +4923,7 @@
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢潕</t>
         </is>
       </c>
@@ -4991,8 +4988,7 @@
       </c>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞⌇
-‹</t>
+          <t xml:space="preserve">㳞⌇</t>
         </is>
       </c>
       <c r="K17" s="23"/>
@@ -5054,8 +5050,7 @@
       <c r="I19" s="22"/>
       <c r="J19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="K19" s="22"/>
@@ -5206,8 +5201,7 @@
       </c>
       <c r="J23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞⌇
-‹</t>
+          <t xml:space="preserve">㳞⌇</t>
         </is>
       </c>
       <c r="K23" s="22"/>

--- a/sheets/대금율보/검수/검정고무신.xlsx
+++ b/sheets/대금율보/검수/검정고무신.xlsx
@@ -4310,22 +4310,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="88.89" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="69.14" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="69.14" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="69.14" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="69.14" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="K6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="69.14" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="69.14" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
       <c r="J8" s="21"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="69.14" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="69.14" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="26"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="K10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="69.14" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="69.14" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="24" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
       <c r="J12" s="21"/>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="69.14" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="69.14" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="K14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="69.14" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="69.14" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="69.14" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="69.14" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="26"/>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="K18" s="27"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="69.14" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="K19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="69.14" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="K20" s="23"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="69.14" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="K21" s="23"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="69.14" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="26"/>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="K22" s="26"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="69.14" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="K23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="69.14" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="K24" s="23"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="69.14" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="26"/>
@@ -5283,6 +5283,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="55"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="45"/>
 </worksheet>
 </file>